--- a/artfynd/A 18788-2024 artfynd.xlsx
+++ b/artfynd/A 18788-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120144013</v>
+        <v>120144030</v>
       </c>
       <c r="B2" t="n">
-        <v>108787</v>
+        <v>108827</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>220320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120144030</v>
+        <v>120144013</v>
       </c>
       <c r="B3" t="n">
-        <v>108827</v>
+        <v>108787</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220320</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/artfynd/A 18788-2024 artfynd.xlsx
+++ b/artfynd/A 18788-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120144030</v>
       </c>
       <c r="B2" t="n">
-        <v>108827</v>
+        <v>108851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>120144013</v>
       </c>
       <c r="B3" t="n">
-        <v>108787</v>
+        <v>108811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18788-2024 artfynd.xlsx
+++ b/artfynd/A 18788-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120144030</v>
+        <v>120144013</v>
       </c>
       <c r="B2" t="n">
-        <v>108851</v>
+        <v>108811</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220320</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120144013</v>
+        <v>120144030</v>
       </c>
       <c r="B3" t="n">
-        <v>108811</v>
+        <v>108851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>220320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/artfynd/A 18788-2024 artfynd.xlsx
+++ b/artfynd/A 18788-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120144013</v>
+        <v>120144030</v>
       </c>
       <c r="B2" t="n">
-        <v>108811</v>
+        <v>108851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>220320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120144030</v>
+        <v>120144013</v>
       </c>
       <c r="B3" t="n">
-        <v>108851</v>
+        <v>108811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220320</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
